--- a/new-info35/web.xlsx
+++ b/new-info35/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="17175" windowHeight="8925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="14" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
   <si>
     <t>domain</t>
   </si>
@@ -42,6 +42,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>read.bellwether.cloud</t>
     </r>
     <r>
@@ -58,95 +65,67 @@
     <t>#145f39</t>
   </si>
   <si>
-    <r>
-      <t>sec.bellwether.cloud</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
+    <t>spuddles.fun</t>
+  </si>
+  <si>
+    <t>#707899</t>
+  </si>
+  <si>
+    <t>moilfuns.fun</t>
+  </si>
+  <si>
+    <t>#70c588</t>
+  </si>
+  <si>
+    <t>color1</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>play.pixelink.cloud</t>
+  </si>
+  <si>
+    <t>#aa9649</t>
+  </si>
+  <si>
+    <t>sec.pixelink.cloud</t>
+  </si>
+  <si>
+    <t>#b65458</t>
+  </si>
+  <si>
+    <t>play.vortegame.cloud</t>
+  </si>
+  <si>
+    <t>#ddbb99</t>
+  </si>
+  <si>
+    <t>play.mettas.site</t>
+  </si>
+  <si>
+    <t>#957aa9</t>
+  </si>
+  <si>
+    <t>sec.mettas.site</t>
   </si>
   <si>
     <t>#33325d</t>
   </si>
   <si>
-    <r>
-      <t>info.bellwether.cloud</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
+    <t>play.derives.cloud</t>
+  </si>
+  <si>
+    <t>#4189b3</t>
+  </si>
+  <si>
+    <t>sec.derives.cloud</t>
   </si>
   <si>
     <t>#ae1c31</t>
-  </si>
-  <si>
-    <t>spuddles.fun</t>
-  </si>
-  <si>
-    <t>#707899</t>
-  </si>
-  <si>
-    <t>moilfuns.fun</t>
-  </si>
-  <si>
-    <t>#70c588</t>
-  </si>
-  <si>
-    <t>color1</t>
-  </si>
-  <si>
-    <t>info</t>
-  </si>
-  <si>
-    <t>json</t>
-  </si>
-  <si>
-    <t>play.pixelink.cloud</t>
-  </si>
-  <si>
-    <t>#aa9649</t>
-  </si>
-  <si>
-    <t>sec.pixelink.cloud</t>
-  </si>
-  <si>
-    <t>#b65458</t>
-  </si>
-  <si>
-    <t>play.vortegame.cloud</t>
-  </si>
-  <si>
-    <t>#ddbb99</t>
-  </si>
-  <si>
-    <t>play.mettas.site</t>
-  </si>
-  <si>
-    <t>#957aa9</t>
-  </si>
-  <si>
-    <t>sec.mettas.site</t>
-  </si>
-  <si>
-    <t>play.derives.cloud</t>
-  </si>
-  <si>
-    <t>#4189b3</t>
-  </si>
-  <si>
-    <t>sec.derives.cloud</t>
   </si>
   <si>
     <t>lagoonsea.com</t>
@@ -441,7 +420,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="50">
+  <fills count="51">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -529,6 +508,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDBB99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF145F39"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -876,7 +861,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -900,16 +885,16 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -918,85 +903,85 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1072,10 +1057,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1087,10 +1072,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1503,21 +1488,13 @@
       <c r="C2" s="26"/>
     </row>
     <row r="3" ht="16.5" spans="1:7">
-      <c r="A3" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>6</v>
-      </c>
+      <c r="A3" s="24"/>
+      <c r="B3" s="27"/>
       <c r="C3" s="26"/>
     </row>
     <row r="4" ht="16.5" spans="1:7">
-      <c r="A4" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>8</v>
-      </c>
+      <c r="A4" s="24"/>
+      <c r="B4" s="28"/>
       <c r="C4" s="26"/>
     </row>
     <row r="6" spans="1:7">
@@ -1527,25 +1504,24 @@
     </row>
     <row r="16" spans="1:7">
       <c r="F16" s="29" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G16" s="30" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="6:7">
       <c r="F17" s="29" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F16" r:id="rId1" display="spuddles.fun"/>
     <hyperlink ref="F17" r:id="rId2" display="moilfuns.fun"/>
-    <hyperlink ref="A6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1566,24 +1542,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="15" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2">
@@ -1595,10 +1571,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3">
@@ -1610,10 +1586,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4">
@@ -1672,24 +1648,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="11" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2">
@@ -1701,10 +1677,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3">
@@ -1716,10 +1692,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="15" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4">
@@ -1731,10 +1707,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5">
@@ -1777,24 +1753,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2">
@@ -1806,10 +1782,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3">
@@ -1821,10 +1797,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4">
@@ -1836,10 +1812,10 @@
     </row>
     <row r="5" ht="15" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5">
@@ -1852,10 +1828,10 @@
     </row>
     <row r="6" ht="15" spans="1:6">
       <c r="A6" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6">

--- a/new-info35/web.xlsx
+++ b/new-info35/web.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
   <si>
     <t>domain</t>
   </si>
@@ -41,28 +41,16 @@
     <t>color2</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>read.bellwether.cloud</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>#145f39</t>
+    <t>sec.bellwether.cloud</t>
+  </si>
+  <si>
+    <t>#33325d</t>
+  </si>
+  <si>
+    <t>info.bellwether.cloud</t>
+  </si>
+  <si>
+    <t>#ae1c31</t>
   </si>
   <si>
     <t>spuddles.fun</t>
@@ -113,9 +101,6 @@
     <t>sec.mettas.site</t>
   </si>
   <si>
-    <t>#33325d</t>
-  </si>
-  <si>
     <t>play.derives.cloud</t>
   </si>
   <si>
@@ -123,9 +108,6 @@
   </si>
   <si>
     <t>sec.derives.cloud</t>
-  </si>
-  <si>
-    <t>#ae1c31</t>
   </si>
   <si>
     <t>lagoonsea.com</t>
@@ -168,7 +150,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="33">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -413,14 +395,8 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="51">
+  <fills count="50">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -508,12 +484,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDBB99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF145F39"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -861,7 +831,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -885,16 +855,16 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -903,89 +873,89 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1054,28 +1024,25 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1461,7 +1428,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="27.75" customWidth="1"/>
@@ -1488,40 +1455,39 @@
       <c r="C2" s="26"/>
     </row>
     <row r="3" ht="16.5" spans="1:7">
-      <c r="A3" s="24"/>
-      <c r="B3" s="27"/>
+      <c r="A3" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>6</v>
+      </c>
       <c r="C3" s="26"/>
     </row>
-    <row r="4" ht="16.5" spans="1:7">
-      <c r="A4" s="24"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="26"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
+    <row r="5" spans="1:7">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="F15" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="29" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="F16" s="29" t="s">
-        <v>5</v>
+      <c r="F16" s="28" t="s">
+        <v>9</v>
       </c>
       <c r="G16" s="30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="6:7">
-      <c r="F17" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="31" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F16" r:id="rId1" display="spuddles.fun"/>
-    <hyperlink ref="F17" r:id="rId2" display="moilfuns.fun"/>
+    <hyperlink ref="F15" r:id="rId1" display="spuddles.fun"/>
+    <hyperlink ref="F16" r:id="rId2" display="moilfuns.fun"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1542,24 +1508,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2">
@@ -1571,10 +1537,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3">
@@ -1586,10 +1552,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4">
@@ -1648,24 +1614,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2">
@@ -1677,10 +1643,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3">
@@ -1692,10 +1658,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4">
@@ -1707,10 +1673,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5">
@@ -1753,16 +1719,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:6">

--- a/new-info35/web.xlsx
+++ b/new-info35/web.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>domain</t>
   </si>
@@ -39,6 +39,12 @@
   </si>
   <si>
     <t>color2</t>
+  </si>
+  <si>
+    <t>read.bellwether.cloud</t>
+  </si>
+  <si>
+    <t>#145f39</t>
   </si>
   <si>
     <t>sec.bellwether.cloud</t>
@@ -396,7 +402,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="50">
+  <fills count="51">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -484,6 +490,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDBB99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF145F39"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -831,7 +843,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -855,16 +867,16 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -873,89 +885,89 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1027,10 +1039,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1039,10 +1054,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1428,7 +1443,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="27.75" customWidth="1"/>
@@ -1445,49 +1460,63 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:7">
+    <row r="2" spans="1:7">
       <c r="A2" s="24" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="26"/>
     </row>
     <row r="3" ht="16.5" spans="1:7">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="26"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="F15" s="28" t="s">
+      <c r="C3" s="27"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:7">
+      <c r="A4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="29" t="s">
+      <c r="B4" s="28" t="s">
         <v>8</v>
       </c>
+      <c r="C4" s="27"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="24"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="24"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="F16" s="28" t="s">
+      <c r="F16" s="29" t="s">
         <v>9</v>
       </c>
       <c r="G16" s="30" t="s">
         <v>10</v>
       </c>
     </row>
+    <row r="17" spans="6:7">
+      <c r="F17" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F15" r:id="rId1" display="spuddles.fun"/>
-    <hyperlink ref="F16" r:id="rId2" display="moilfuns.fun"/>
+    <hyperlink ref="F16" r:id="rId1" display="spuddles.fun"/>
+    <hyperlink ref="F17" r:id="rId2" display="moilfuns.fun"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1508,24 +1537,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2">
@@ -1537,10 +1566,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3">
@@ -1552,10 +1581,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4">
@@ -1614,24 +1643,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2">
@@ -1643,10 +1672,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3">
@@ -1658,10 +1687,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4">
@@ -1673,10 +1702,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5">
@@ -1719,24 +1748,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2">
@@ -1748,10 +1777,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3">
@@ -1763,10 +1792,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4">
@@ -1778,10 +1807,10 @@
     </row>
     <row r="5" ht="15" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5">
@@ -1794,10 +1823,10 @@
     </row>
     <row r="6" ht="15" spans="1:6">
       <c r="A6" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6">

--- a/new-info35/web.xlsx
+++ b/new-info35/web.xlsx
@@ -53,49 +53,49 @@
     <t>#33325d</t>
   </si>
   <si>
+    <t>spuddles.fun</t>
+  </si>
+  <si>
+    <t>#707899</t>
+  </si>
+  <si>
+    <t>moilfuns.fun</t>
+  </si>
+  <si>
+    <t>#70c588</t>
+  </si>
+  <si>
+    <t>color1</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>play.pixelink.cloud</t>
+  </si>
+  <si>
+    <t>#aa9649</t>
+  </si>
+  <si>
+    <t>sec.pixelink.cloud</t>
+  </si>
+  <si>
+    <t>#b65458</t>
+  </si>
+  <si>
+    <t>play.vortegame.cloud</t>
+  </si>
+  <si>
+    <t>#ddbb99</t>
+  </si>
+  <si>
     <t>info.bellwether.cloud</t>
   </si>
   <si>
     <t>#ae1c31</t>
-  </si>
-  <si>
-    <t>spuddles.fun</t>
-  </si>
-  <si>
-    <t>#707899</t>
-  </si>
-  <si>
-    <t>moilfuns.fun</t>
-  </si>
-  <si>
-    <t>#70c588</t>
-  </si>
-  <si>
-    <t>color1</t>
-  </si>
-  <si>
-    <t>info</t>
-  </si>
-  <si>
-    <t>json</t>
-  </si>
-  <si>
-    <t>play.pixelink.cloud</t>
-  </si>
-  <si>
-    <t>#aa9649</t>
-  </si>
-  <si>
-    <t>sec.pixelink.cloud</t>
-  </si>
-  <si>
-    <t>#b65458</t>
-  </si>
-  <si>
-    <t>play.vortegame.cloud</t>
-  </si>
-  <si>
-    <t>#ddbb99</t>
   </si>
   <si>
     <t>play.mettas.site</t>
@@ -967,7 +967,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1036,9 +1036,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1046,9 +1050,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1461,10 +1462,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="27" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1472,19 +1473,13 @@
       <c r="A3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="27"/>
+      <c r="C3" s="29"/>
     </row>
     <row r="4" ht="16.5" spans="1:7">
-      <c r="A4" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="27"/>
+      <c r="C4" s="29"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="15"/>
@@ -1492,25 +1487,25 @@
       <c r="C6" s="15"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="24"/>
+      <c r="A11" s="15"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="24"/>
+      <c r="A12" s="15"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="F16" s="29" t="s">
+      <c r="F16" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="6:7">
+      <c r="F17" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="G16" s="30" t="s">
+      <c r="G17" s="32" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="6:7">
-      <c r="F17" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="31" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1526,8 +1521,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
   </cols>
@@ -1537,24 +1532,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2">
@@ -1566,10 +1561,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3">
@@ -1581,10 +1576,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4">
@@ -1595,7 +1590,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="9"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -1610,6 +1605,18 @@
     </row>
     <row r="7" spans="1:5">
       <c r="C7" s="23"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="26"/>
+      <c r="B21" s="26"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1643,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1705,7 +1712,7 @@
         <v>27</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5">
@@ -1748,16 +1755,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:6">
